--- a/site/exports/bnu-chemistry.xlsx
+++ b/site/exports/bnu-chemistry.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,65 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>化学学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>当前在岗/全职人事状态未独立证明；教授栏目、旧至今措辞及导师资格不独立证明现职。；校区及院系法定行政父级未知，不推断直属或默认校区。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -720,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1375,8 +1429,321 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>北京化工大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>原文仅学位/教育标签或学习区间，没有可采纳的明确授位动词；不由毕业、博士后或导师资格推定授位。；机构地理分类不代表国籍或实际所在地；985为历史39校固定分类。保留来源院校名称，不推断未披露授位法人。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源院系：化学工程学院；规范专业未明确。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>原文仅学位/教育标签或学习区间，没有可采纳的明确授位动词；不由毕业、博士后或导师资格推定授位。；机构地理分类不代表国籍或实际所在地；985为历史39校固定分类。保留来源院校名称，不推断未披露授位法人。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源院系：化学系；规范专业未明确。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>加拿大多伦多大学</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>明确非授位研究/访问事件；false仅描述本事件，不否认潜在的底层学位。；机构地理分类不代表国籍或实际所在地；985为历史39校固定分类。保留来源院校名称，不推断未披露授位法人。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>美国西北大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>明确非授位研究/访问事件；false仅描述本事件，不否认潜在的底层学位。；机构地理分类不代表国籍或实际所在地；985为历史39校固定分类。保留来源院校名称，不推断未披露授位法人。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学化学学院</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源source_end_literal：至今</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S11"/>
+  <autoFilter ref="A1:S16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1388,6 +1755,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1399,18 +1771,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="19.6" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16.8" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1478,8 +1850,163 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>李亚栋</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>导师</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>doctoral</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>导师；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Edward Sargent</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>合作导师</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>合作导师；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Edward Sargent</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>合作导师</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>合作导师；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L4"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1490,18 +2017,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="36.4" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
-    <col width="61.59999999999999" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1805,8 +2332,116 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Electrified synthesis of n-propanol using a dilute alloy catalyst</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_source_order：Y. Chen、X. Wang、X.-Y. Li、R. K. Miao、J. Dong、Z. Zhao、C. Liu、J. E. Huang、J. Wu、S. Chu、W. Ni、Z. Guo、Y. Xu、P. Ou、B. Xu、Y. Hou、D. Sinton、E. Sargent；来源书目信息（卷）：8；来源书目信息（pages_or_article_number）：239-247</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Efficient multicarbon formation in acidic CO2 reduction via tandem electrocatalysis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-023-01543-8</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_source_order：Y. Chen、X. Li、Z. Chen、A. Ozden、J. Huang、P. Ou、J. Dong、J. Zhang、C. Tian、B. Lee、X. Wang、S. Liu、Q. Qu、S. Wang、Y. Xu、R. Miao、Y. Zhao、Y. Liu、C. Qiu、J. Abed、H. Liu、H. Shin、D. Wang、Y. Li、D. Sinton、E. Sargent；来源书目信息（卷）：19；来源书目信息（pages_or_article_number）：311-318；来源书目信息（online_publication_date）：2023-11-23；来源书目信息（issue_date）：2024-03；来源书目信息（date_note）：官网书目2024为卷期年；原刊online/VOR为2023-11-23，分开保留。；来源书目信息（publisher_author_names）：Yuanjun Chen；Xiao-Yan Li；Zhu Chen；Adnan Ozden；Jianan Erick Huang；Pengfei Ou；Juncai Dong；Jinqiang Zhang；Cong Tian；Byoung-Hoon Lee；Xinyue Wang；Shijie Liu；Qingyun Qu；Sasa Wang；Yi Xu；Rui Kai Miao；Yong Zhao；Yanjiang Liu；Chenyue Qiu；Jehad Abed；Hengzhou Liu；Heejong Shin；Dingsheng Wang；Yadong Li；David Sinton；Edward H. Sargent；来源书目信息（publisher_target_affiliation）：Department of Electrical and Computer Engineering, University of Toronto</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1820,6 +2455,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1831,14 +2470,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="32.2" customWidth="1" min="2" max="2"/>
+    <col width="64.39999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2243,8 +2882,193 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-chenyuanjun-s001-3e4898459bdb</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:39:06Z</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-chenyuanjun-s002-464d563b5359</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>https://chem2.bnu.edu.cn/szll/jsdw/wjhxyjs/js/bc302ce51ac84474855e7facfb90f213.html</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:39:21Z</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-chenyuanjun-s003-d73889b6e146</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41565-023-01543-8</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:40:11.575Z</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-chenyuanjun-s004-f41a96bba22b</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41929-025-01301-0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:40:04.104Z</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>陈远均</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-chenyuanjun-s005-f41a96bba22b</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41929-025-01301-0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:39:53Z</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -2257,6 +3081,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
